--- a/INSTANCES/instances_xlsx/A_MTN_3/379FL_15A_2.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_3/379FL_15A_2.xlsx
@@ -12020,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -12054,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -12071,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -12088,7 +12088,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -12122,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -12156,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -12173,7 +12173,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -12190,7 +12190,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -12224,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -12258,7 +12258,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
